--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>16/06/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>731</v>
+        <v>713</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>16/06/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,43 +472,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>632</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>16/06/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>16/06/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>404</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>16/06/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>16/06/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>390</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>16/06/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>293</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>16/06/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>275</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>16/06/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>16/06/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>16/06/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>16/06/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>16/06/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16/06/2025</t>
+          <t>17/06/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>713</v>
+        <v>696</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16/06/2025</t>
+          <t>17/06/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>615</v>
+        <v>628</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16/06/2025</t>
+          <t>17/06/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16/06/2025</t>
+          <t>17/06/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,43 +502,43 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16/06/2025</t>
+          <t>17/06/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16/06/2025</t>
+          <t>17/06/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16/06/2025</t>
+          <t>17/06/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16/06/2025</t>
+          <t>17/06/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16/06/2025</t>
+          <t>17/06/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16/06/2025</t>
+          <t>17/06/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16/06/2025</t>
+          <t>17/06/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,37 +607,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16/06/2025</t>
+          <t>17/06/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16/06/2025</t>
+          <t>17/06/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>696</v>
+        <v>707</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>628</v>
+        <v>646</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5">
@@ -498,11 +498,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6">
@@ -513,11 +513,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -448,37 +448,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>707</v>
+        <v>691</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,28 +487,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,28 +517,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>691</v>
+        <v>729</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,7 +478,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,58 +487,58 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>338</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>729</v>
+        <v>753</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>649</v>
+        <v>663</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>487</v>
+        <v>506</v>
       </c>
     </row>
     <row r="5">
@@ -498,11 +498,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>418</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6">
@@ -513,11 +513,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>417</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>753</v>
+        <v>776</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>663</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>428</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>427</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>395</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>293</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -628,7 +628,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>776</v>
+        <v>784</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>610</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>514</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>303</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>784</v>
+        <v>877</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>650</v>
+        <v>688</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>417</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>400</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>384</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>319</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>877</v>
+        <v>907</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>688</v>
+        <v>697</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,43 +487,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>494</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>388</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>345</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,7 +637,18 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>07/07/2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>907</v>
+        <v>911</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>697</v>
+        <v>708</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,43 +487,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>373</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,18 +532,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -553,7 +553,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>238</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>911</v>
+        <v>950</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,43 +472,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>708</v>
+        <v>813</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>460</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>383</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>365</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,18 +562,18 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>229</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -583,22 +583,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,48 +607,48 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>950</v>
+        <v>957</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>813</v>
+        <v>825</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>449</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>431</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6">
@@ -513,11 +513,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>376</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7">
@@ -528,11 +528,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>957</v>
+        <v>937</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>825</v>
+        <v>835</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>419</v>
+        <v>438</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>360</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>328</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -638,17 +638,6 @@
       </c>
       <c r="C14" t="n">
         <v>88</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>10/07/2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>937</v>
+        <v>947</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>835</v>
+        <v>857</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -588,11 +588,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12">
@@ -603,11 +603,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>947</v>
+        <v>918</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>435</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>918</v>
+        <v>975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>855</v>
+        <v>842</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,43 +487,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>390</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>310</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>975</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,43 +502,43 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>397</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>376</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>337</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1032</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>866</v>
+        <v>870</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>465</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>353</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>314</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,43 +547,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>281</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -598,7 +598,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1005</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>870</v>
+        <v>827</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>354</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,58 +517,58 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>337</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>328</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,28 +577,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -638,6 +638,17 @@
       </c>
       <c r="C14" t="n">
         <v>75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>22/07/2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1016</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>827</v>
+        <v>818</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>489</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,133 +502,133 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>321</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,18 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>22/07/2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1105</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,7 +478,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>445</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>333</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>292</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>290</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,28 +547,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,28 +592,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1080</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>818</v>
+        <v>792</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,43 +487,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>463</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>345</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>302</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,88 +532,88 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>169</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,7 +637,18 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>31/07/2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1035</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>792</v>
+        <v>787</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>436</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,118 +517,118 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>195</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>169</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,18 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>31/07/2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>1</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/quantidade_processos.xlsx
+++ b/quantidade_processos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1100</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,58 +472,58 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>787</v>
+        <v>885</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>408</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>293</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>193</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,73 +562,73 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>183</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>144</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>130</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,7 +637,18 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>104</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
